--- a/idecba/autoservicios.xlsx
+++ b/idecba/autoservicios.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16245" windowHeight="7065"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="AC_M_01" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="59">
   <si>
     <t>Período</t>
   </si>
@@ -225,7 +225,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/febrero de 2026</t>
+    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/marzo de 2026</t>
   </si>
 </sst>
 </file>
@@ -942,7 +942,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="37"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="36" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1026,7 +1026,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
     </xf>
@@ -1402,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="24" customWidth="1"/>
@@ -1411,12 +1410,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="35"/>
+      <c r="B1" s="34"/>
       <c r="C1" s="23"/>
-      <c r="D1" s="33"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="23"/>
       <c r="F1" s="23"/>
       <c r="G1" s="23"/>
@@ -2361,7 +2360,7 @@
       <c r="D96" s="29"/>
       <c r="E96" s="32"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="30" t="s">
         <v>4</v>
       </c>
@@ -2371,7 +2370,7 @@
       <c r="D97" s="29"/>
       <c r="E97" s="32"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="30" t="s">
         <v>5</v>
       </c>
@@ -2381,7 +2380,7 @@
       <c r="D98" s="29"/>
       <c r="E98" s="32"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="24" t="s">
         <v>6</v>
       </c>
@@ -2391,7 +2390,7 @@
       <c r="D99" s="29"/>
       <c r="E99" s="32"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="24" t="s">
         <v>7</v>
       </c>
@@ -2401,7 +2400,7 @@
       <c r="D100" s="29"/>
       <c r="E100" s="32"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="24" t="s">
         <v>8</v>
       </c>
@@ -2411,7 +2410,7 @@
       <c r="D101" s="29"/>
       <c r="E101" s="32"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="24" t="s">
         <v>9</v>
       </c>
@@ -2421,7 +2420,7 @@
       <c r="D102" s="29"/>
       <c r="E102" s="32"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="24" t="s">
         <v>31</v>
       </c>
@@ -2431,7 +2430,7 @@
       <c r="D103" s="29"/>
       <c r="E103" s="32"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="24" t="s">
         <v>32</v>
       </c>
@@ -2441,7 +2440,7 @@
       <c r="D104" s="29"/>
       <c r="E104" s="32"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="30" t="s">
         <v>33</v>
       </c>
@@ -2451,7 +2450,7 @@
       <c r="D105" s="29"/>
       <c r="E105" s="32"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="30" t="s">
         <v>34</v>
       </c>
@@ -2461,7 +2460,7 @@
       <c r="D106" s="29"/>
       <c r="E106" s="32"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="14">
         <v>2026</v>
       </c>
@@ -2469,7 +2468,7 @@
       <c r="D107" s="29"/>
       <c r="E107" s="32"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="30" t="s">
         <v>2</v>
       </c>
@@ -2479,7 +2478,7 @@
       <c r="D108" s="29"/>
       <c r="E108" s="32"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="30" t="s">
         <v>3</v>
       </c>
@@ -2487,41 +2486,49 @@
         <v>-20.169342212697451</v>
       </c>
     </row>
-    <row r="110" spans="1:6" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="38" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B110" s="31">
+        <v>-21.848684540786156</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B110" s="38"/>
-    </row>
-    <row r="111" spans="1:6" s="15" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="36" t="s">
+      <c r="B111" s="37"/>
+    </row>
+    <row r="112" spans="1:5" s="15" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B111" s="36"/>
-    </row>
-    <row r="112" spans="1:6" s="15" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="36" t="s">
+      <c r="B112" s="35"/>
+    </row>
+    <row r="113" spans="1:6" s="15" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B112" s="36"/>
-      <c r="D112" s="37"/>
-      <c r="E112" s="37"/>
-      <c r="F112" s="37"/>
-    </row>
-    <row r="113" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="34" t="s">
+      <c r="B113" s="35"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+    </row>
+    <row r="114" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B113" s="34"/>
+      <c r="B114" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="A111:B111"/>
     <mergeCell ref="A112:B112"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A111:B111"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -2542,10 +2549,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="40"/>
+      <c r="B1" s="39"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -2629,7 +2636,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -2637,7 +2644,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>

--- a/idecba/autoservicios.xlsx
+++ b/idecba/autoservicios.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\AUTOSERVICIOS MAYORISTAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="AC_M_01" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
   <si>
     <t>Período</t>
   </si>
@@ -225,7 +225,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/marzo de 2026</t>
+    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/abril de 2026</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="24" customWidth="1"/>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="30" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B85" s="31">
         <v>-15.262764561510178</v>
@@ -2494,41 +2494,49 @@
         <v>-21.848684540786156</v>
       </c>
     </row>
-    <row r="111" spans="1:5" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="37" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" s="31">
+        <v>-19.010841314069825</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B111" s="37"/>
-    </row>
-    <row r="112" spans="1:5" s="15" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="35" t="s">
+      <c r="B112" s="37"/>
+    </row>
+    <row r="113" spans="1:6" s="15" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B112" s="35"/>
-    </row>
-    <row r="113" spans="1:6" s="15" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="35" t="s">
+      <c r="B113" s="35"/>
+    </row>
+    <row r="114" spans="1:6" s="15" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B113" s="35"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="36"/>
-      <c r="F113" s="36"/>
-    </row>
-    <row r="114" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="33" t="s">
+      <c r="B114" s="35"/>
+      <c r="D114" s="36"/>
+      <c r="E114" s="36"/>
+      <c r="F114" s="36"/>
+    </row>
+    <row r="115" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B114" s="33"/>
+      <c r="B115" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="A112:B112"/>
     <mergeCell ref="A113:B113"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A112:B112"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -2636,7 +2644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -2644,7 +2652,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>

--- a/idecba/autoservicios.xlsx
+++ b/idecba/autoservicios.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="AC_M_01" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="59">
   <si>
     <t>Período</t>
   </si>
@@ -225,7 +225,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/abril de 2026</t>
+    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/mayo de 2026</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="24" customWidth="1"/>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="24" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B86" s="31">
         <v>-4.7410937379388507</v>
@@ -2473,7 +2473,7 @@
         <v>2</v>
       </c>
       <c r="B108" s="31">
-        <v>-21.531749986173544</v>
+        <v>-21.531699027082464</v>
       </c>
       <c r="D108" s="29"/>
       <c r="E108" s="32"/>
@@ -2483,7 +2483,7 @@
         <v>3</v>
       </c>
       <c r="B109" s="31">
-        <v>-20.169342212697451</v>
+        <v>-20.1692333964839</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -2491,7 +2491,7 @@
         <v>4</v>
       </c>
       <c r="B110" s="31">
-        <v>-21.848684540786156</v>
+        <v>-21.848504496160391</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -2502,41 +2502,49 @@
         <v>-19.010841314069825</v>
       </c>
     </row>
-    <row r="112" spans="1:5" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="37" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="31">
+        <v>-13.224133014837946</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B112" s="37"/>
-    </row>
-    <row r="113" spans="1:6" s="15" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="35" t="s">
+      <c r="B113" s="37"/>
+    </row>
+    <row r="114" spans="1:6" s="15" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B113" s="35"/>
-    </row>
-    <row r="114" spans="1:6" s="15" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="35" t="s">
+      <c r="B114" s="35"/>
+    </row>
+    <row r="115" spans="1:6" s="15" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B114" s="35"/>
-      <c r="D114" s="36"/>
-      <c r="E114" s="36"/>
-      <c r="F114" s="36"/>
-    </row>
-    <row r="115" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="33" t="s">
+      <c r="B115" s="35"/>
+      <c r="D115" s="36"/>
+      <c r="E115" s="36"/>
+      <c r="F115" s="36"/>
+    </row>
+    <row r="116" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B115" s="33"/>
+      <c r="B116" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="A113:B113"/>
     <mergeCell ref="A114:B114"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="A113:B113"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/idecba/autoservicios.xlsx
+++ b/idecba/autoservicios.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12180" windowHeight="9495"/>
   </bookViews>
   <sheets>
     <sheet name="AC_M_01" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="59">
   <si>
     <t>Período</t>
   </si>
@@ -225,7 +225,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/mayo de 2026</t>
+    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/junio de 2026</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="24" customWidth="1"/>
@@ -2205,7 +2205,7 @@
         <v>56</v>
       </c>
       <c r="B81" s="27">
-        <v>-8.2820536692800424</v>
+        <v>-8.2820361071176745</v>
       </c>
       <c r="D81" s="29"/>
       <c r="E81" s="32"/>
@@ -2245,7 +2245,7 @@
         <v>38</v>
       </c>
       <c r="B85" s="31">
-        <v>-15.262764561510178</v>
+        <v>-15.262764561510235</v>
       </c>
       <c r="D85" s="29"/>
       <c r="E85" s="32"/>
@@ -2255,14 +2255,14 @@
         <v>39</v>
       </c>
       <c r="B86" s="31">
-        <v>-4.7410937379388507</v>
+        <v>-4.7410937379388844</v>
       </c>
       <c r="D86" s="29"/>
       <c r="E86" s="32"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="24" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B87" s="31">
         <v>-2.1395496917393841</v>
@@ -2275,7 +2275,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="31">
-        <v>-12.361662312467359</v>
+        <v>-12.36166231246737</v>
       </c>
       <c r="D88" s="29"/>
       <c r="E88" s="32"/>
@@ -2295,7 +2295,7 @@
         <v>31</v>
       </c>
       <c r="B90" s="31">
-        <v>-16.910087158052377</v>
+        <v>-16.909954894138192</v>
       </c>
       <c r="D90" s="29"/>
       <c r="E90" s="32"/>
@@ -2305,7 +2305,7 @@
         <v>32</v>
       </c>
       <c r="B91" s="31">
-        <v>-20.38999728219806</v>
+        <v>-20.389923446181978</v>
       </c>
       <c r="D91" s="29"/>
       <c r="E91" s="32"/>
@@ -2315,7 +2315,7 @@
         <v>33</v>
       </c>
       <c r="B92" s="31">
-        <v>2.1087166702506988</v>
+        <v>2.1087278751732885</v>
       </c>
       <c r="D92" s="29"/>
       <c r="E92" s="32"/>
@@ -2325,7 +2325,7 @@
         <v>34</v>
       </c>
       <c r="B93" s="31">
-        <v>-14.369999346488049</v>
+        <v>-14.37002480783609</v>
       </c>
       <c r="D93" s="29"/>
       <c r="E93" s="32"/>
@@ -2335,7 +2335,7 @@
         <v>57</v>
       </c>
       <c r="B94" s="27">
-        <v>-12.773686119727213</v>
+        <v>-12.773669137037425</v>
       </c>
       <c r="D94" s="29"/>
       <c r="E94" s="32"/>
@@ -2345,7 +2345,7 @@
         <v>2</v>
       </c>
       <c r="B95" s="31">
-        <v>-8.4917351624114961</v>
+        <v>-8.4917283142703752</v>
       </c>
       <c r="D95" s="29"/>
       <c r="E95" s="32"/>
@@ -2355,7 +2355,7 @@
         <v>3</v>
       </c>
       <c r="B96" s="31">
-        <v>-7.325089694835329</v>
+        <v>-7.3250791701568785</v>
       </c>
       <c r="D96" s="29"/>
       <c r="E96" s="32"/>
@@ -2365,7 +2365,7 @@
         <v>4</v>
       </c>
       <c r="B97" s="31">
-        <v>-2.3302272857465112</v>
+        <v>-2.3301747814481577</v>
       </c>
       <c r="D97" s="29"/>
       <c r="E97" s="32"/>
@@ -2375,7 +2375,7 @@
         <v>5</v>
       </c>
       <c r="B98" s="31">
-        <v>-7.4082474073589033E-3</v>
+        <v>-7.301866744868768E-3</v>
       </c>
       <c r="D98" s="29"/>
       <c r="E98" s="32"/>
@@ -2385,7 +2385,7 @@
         <v>6</v>
       </c>
       <c r="B99" s="31">
-        <v>-2.4969459014065665</v>
+        <v>-2.496863550821582</v>
       </c>
       <c r="D99" s="29"/>
       <c r="E99" s="32"/>
@@ -2395,7 +2395,7 @@
         <v>7</v>
       </c>
       <c r="B100" s="31">
-        <v>-12.542631704322538</v>
+        <v>-12.542596010960983</v>
       </c>
       <c r="D100" s="29"/>
       <c r="E100" s="32"/>
@@ -2405,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="B101" s="31">
-        <v>-8.1873214162719208</v>
+        <v>-8.1872538523662381</v>
       </c>
       <c r="D101" s="29"/>
       <c r="E101" s="32"/>
@@ -2415,7 +2415,7 @@
         <v>9</v>
       </c>
       <c r="B102" s="31">
-        <v>-10.173824246212625</v>
+        <v>-10.173774932772639</v>
       </c>
       <c r="D102" s="29"/>
       <c r="E102" s="32"/>
@@ -2425,7 +2425,7 @@
         <v>31</v>
       </c>
       <c r="B103" s="31">
-        <v>-28.633124541941168</v>
+        <v>-28.633199826777421</v>
       </c>
       <c r="D103" s="29"/>
       <c r="E103" s="32"/>
@@ -2435,7 +2435,7 @@
         <v>32</v>
       </c>
       <c r="B104" s="31">
-        <v>-25.521895953015871</v>
+        <v>-25.521952359682366</v>
       </c>
       <c r="D104" s="29"/>
       <c r="E104" s="32"/>
@@ -2445,7 +2445,7 @@
         <v>33</v>
       </c>
       <c r="B105" s="31">
-        <v>-24.89760732377918</v>
+        <v>-24.897622655474883</v>
       </c>
       <c r="D105" s="29"/>
       <c r="E105" s="32"/>
@@ -2455,7 +2455,7 @@
         <v>34</v>
       </c>
       <c r="B106" s="31">
-        <v>-18.692232974580957</v>
+        <v>-18.692243560122645</v>
       </c>
       <c r="D106" s="29"/>
       <c r="E106" s="32"/>
@@ -2473,7 +2473,7 @@
         <v>2</v>
       </c>
       <c r="B108" s="31">
-        <v>-21.531699027082464</v>
+        <v>-21.531704899360328</v>
       </c>
       <c r="D108" s="29"/>
       <c r="E108" s="32"/>
@@ -2483,7 +2483,7 @@
         <v>3</v>
       </c>
       <c r="B109" s="31">
-        <v>-20.1692333964839</v>
+        <v>-20.169242462508862</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -2491,7 +2491,7 @@
         <v>4</v>
       </c>
       <c r="B110" s="31">
-        <v>-21.848504496160391</v>
+        <v>-21.848546508004119</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -2499,7 +2499,7 @@
         <v>5</v>
       </c>
       <c r="B111" s="31">
-        <v>-19.010841314069825</v>
+        <v>-19.010927477164831</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -2507,44 +2507,52 @@
         <v>6</v>
       </c>
       <c r="B112" s="31">
-        <v>-13.224133014837946</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="37" t="s">
+        <v>-13.239828521901542</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B113" s="31">
+        <v>-20.682735712881861</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B113" s="37"/>
-    </row>
-    <row r="114" spans="1:6" s="15" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="35" t="s">
+      <c r="B114" s="37"/>
+    </row>
+    <row r="115" spans="1:6" s="15" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B114" s="35"/>
-    </row>
-    <row r="115" spans="1:6" s="15" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="35" t="s">
+      <c r="B115" s="35"/>
+    </row>
+    <row r="116" spans="1:6" s="15" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B115" s="35"/>
-      <c r="D115" s="36"/>
-      <c r="E115" s="36"/>
-      <c r="F115" s="36"/>
-    </row>
-    <row r="116" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="33" t="s">
+      <c r="B116" s="35"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="117" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B116" s="33"/>
+      <c r="B117" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="A114:B114"/>
     <mergeCell ref="A115:B115"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A114:B114"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -2602,7 +2610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
@@ -2611,7 +2619,7 @@
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -2627,7 +2635,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>19</v>
       </c>
@@ -2644,7 +2652,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -2676,7 +2684,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
